--- a/output/2026-09-03_04_Italia_Campania_Componentistica-Ventilazione-industriale.xlsx
+++ b/output/2026-09-03_04_Italia_Campania_Componentistica-Ventilazione-industriale.xlsx
@@ -494,7 +494,6 @@
           <t>+39 081 7742627</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Rappresentante/distributore ufficiale ventilatori industriali Nicotra Gebhardt per Campania e sud Italia; sede a Volla (NA).</t>
@@ -616,7 +615,6 @@
           <t>081 7517223</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Distributore all'ingrosso di articoli tecnici industriali e trasmissioni meccaniche; concessionario Bonfiglioli, distributore 3M.</t>
@@ -654,7 +652,6 @@
           <t>081 284427</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Distributore ufficiale per Napoli/Campania di cuscinetti, motoriduttori, motori elettrici e trasmissioni industriali (Siti, Seipee, Dormer Pramet).</t>
@@ -672,7 +669,6 @@
           <t>Eurofluid S.a.s. di Carlo di Martino &amp; C.</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Napoli</t>
@@ -688,7 +684,6 @@
           <t>081 8714899</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Componenti e centrali oleodinamiche (cilindri, valvole). Sede reale verificata: Via Ponte Carmiano 89, Gragnano (NA) - riclassificata da Avellino (fonte originale) a Napoli poiche' indirizzo esatto non era in provincia di Avellino.</t>
@@ -733,7 +728,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Distributore ufficiale MZ Aspiratori per il Sud Italia; ventilatori centrifughi/assiali e aspiratori industriali, magazzino 1.200 mq a Fisciano (SA).</t>
+          <t>Distributore ufficiale MZ Aspiratori per il Sud Italia; ventilatori centrifughi/assiali e aspiratori industriali, magazzino 1.200 mq a Fisciano (SA). [DUPLICATO — vedi anche: 2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -768,10 +763,9 @@
           <t>089 301662</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Forniture industriali dal 2002: cuscinetti, trasmissioni meccaniche, pneumatica, gruppi trattamento aria (SKF, Atlas Copco, Camozzi, Fini).</t>
+          <t>Forniture industriali dal 2002: cuscinetti, trasmissioni meccaniche, pneumatica, gruppi trattamento aria (SKF, Atlas Copco, Camozzi, Fini). [DUPLICATO — vedi anche: 2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -806,7 +800,6 @@
           <t>089 3061220</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Grossista idro-termo-sanitario; rivenditore autorizzato AERMEC e WAVIN Italia per ventilazione meccanica controllata e canalizzazioni.</t>
@@ -844,10 +837,9 @@
           <t>+39 0825 625603</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Forniture industriali da oltre 40 anni: oleodinamica, elettropompe Lowara, cuscinetti SKF, compressori, trasmissioni.</t>
+          <t>Forniture industriali da oltre 40 anni: oleodinamica, elettropompe Lowara, cuscinetti SKF, compressori, trasmissioni. [DUPLICATO — vedi anche: 2026-09-03_00_Italia_Campania_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -882,7 +874,6 @@
           <t>0825 623665 / 0825 624579</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Fornitura industriale di componenti per pneumatica, oleodinamica e automazione; opera in Campania e sud Italia dal 1987.</t>
@@ -920,7 +911,6 @@
           <t>+39 0825 622721</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Fornitore di componenti oleodinamici e pneumatici per l'automazione industriale in Campania dal 2003.</t>
@@ -958,7 +948,6 @@
           <t>0825 446072</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Produzione e fornitura di componenti oleodinamici, raccorderia, pompe e cilindri idraulici dal 1982.</t>
@@ -976,7 +965,6 @@
           <t>Vitillo Srl</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Avellino</t>
@@ -992,7 +980,6 @@
           <t>0825 881555</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Produttore/distributore di componenti oleodinamici e pneumatici (raccorderia, tubi flessibili); sede produttiva ad Ariano Irpino (AV), gruppo con sede principale a Napoli.</t>
@@ -1030,10 +1017,9 @@
           <t>0824 25865</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Forniture industriali dal 1942: compressori e sistemi ad aria compressa, saldatrici, taglio plasma, gas tecnici.</t>
+          <t>Forniture industriali dal 1942: compressori e sistemi ad aria compressa, saldatrici, taglio plasma, gas tecnici. [DUPLICATO — vedi anche: 2026-09-03_00_Italia_Campania_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1068,7 +1054,6 @@
           <t>0824 1664042</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Distribuzione di prodotti termoidraulici, riscaldamento, climatizzazione e sistemi di ventilazione.</t>
@@ -1106,7 +1091,6 @@
           <t>0823 950917</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Vendita di materiale idraulico/termoidraulico, climatizzatori e ricambi condizionatori, Paolisi (BN).</t>
@@ -1166,7 +1150,6 @@
           <t>Gagliardi S.r.l.</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>Caserta</t>
@@ -1182,7 +1165,6 @@
           <t>081 5042757 / 346 5435441</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>Ingrosso e dettaglio di materiale elettrico e termoidraulico dal 1963, Villa di Briano (CE).</t>

--- a/output/2026-09-03_04_Italia_Campania_Componentistica-Ventilazione-industriale.xlsx
+++ b/output/2026-09-03_04_Italia_Campania_Componentistica-Ventilazione-industriale.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
